--- a/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 28,67</t>
+          <t>-7,41; 29,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 11,55</t>
+          <t>-17,84; 12,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,97; 57,91</t>
+          <t>20,1; 57,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 29,13</t>
+          <t>-7,18; 27,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 29,06</t>
+          <t>-4,15; 29,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,38; 57,18</t>
+          <t>28,67; 57,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 25,35</t>
+          <t>-1,92; 23,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 16,86</t>
+          <t>-6,09; 16,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,97; 54,32</t>
+          <t>29,57; 53,06</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 103,34</t>
+          <t>-17,9; 106,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 41,89</t>
+          <t>-43,13; 46,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,63; 217,07</t>
+          <t>50,04; 219,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 119,75</t>
+          <t>-17,64; 109,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 120,89</t>
+          <t>-10,5; 117,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,76; 244,77</t>
+          <t>67,06; 234,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 89,49</t>
+          <t>-6,41; 78,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 60,15</t>
+          <t>-14,86; 55,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,89; 200,82</t>
+          <t>74,49; 191,04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 4,21</t>
+          <t>-24,24; 4,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 4,84</t>
+          <t>-22,04; 5,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,0; 62,26</t>
+          <t>39,78; 61,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 25,33</t>
+          <t>-1,61; 26,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 13,04</t>
+          <t>-10,7; 14,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,78; 67,33</t>
+          <t>47,39; 68,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 10,47</t>
+          <t>-9,45; 11,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 5,97</t>
+          <t>-12,23; 5,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,27; 61,51</t>
+          <t>46,33; 61,32</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 12,25</t>
+          <t>-49,94; 12,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 14,32</t>
+          <t>-44,23; 15,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,43; 185,05</t>
+          <t>77,17; 190,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 88,39</t>
+          <t>-4,18; 96,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 46,09</t>
+          <t>-25,85; 51,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,0; 232,69</t>
+          <t>100,63; 251,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 30,32</t>
+          <t>-22,21; 32,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 17,64</t>
+          <t>-28,41; 17,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100,53; 186,83</t>
+          <t>100,56; 188,57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 21,4</t>
+          <t>-8,45; 21,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 13,18</t>
+          <t>-14,83; 14,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,04; 66,87</t>
+          <t>45,68; 67,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 5,62</t>
+          <t>-22,2; 4,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,69; -1,43</t>
+          <t>-26,13; -1,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,92; 66,58</t>
+          <t>44,64; 65,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 8,64</t>
+          <t>-12,07; 7,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 1,22</t>
+          <t>-17,34; 2,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,9; 63,43</t>
+          <t>48,18; 63,6</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 82,97</t>
+          <t>-22,65; 79,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 51,08</t>
+          <t>-38,16; 58,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103,14; 262,1</t>
+          <t>108,48; 278,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 17,84</t>
+          <t>-52,1; 18,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,03; -3,55</t>
+          <t>-61,88; -5,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99,41; 239,73</t>
+          <t>97,9; 227,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 28,94</t>
+          <t>-29,15; 26,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 3,78</t>
+          <t>-43,04; 7,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>119,01; 216,81</t>
+          <t>112,12; 215,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 27,06</t>
+          <t>-3,03; 27,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 20,58</t>
+          <t>-8,66; 21,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,79; 64,67</t>
+          <t>40,54; 65,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 23,62</t>
+          <t>-5,0; 23,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 34,98</t>
+          <t>5,33; 35,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,67; 72,34</t>
+          <t>49,21; 72,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 21,91</t>
+          <t>0,49; 21,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 23,19</t>
+          <t>1,83; 22,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,68; 65,41</t>
+          <t>48,37; 64,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 107,84</t>
+          <t>-8,53; 115,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 79,95</t>
+          <t>-23,5; 88,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99,61; 269,85</t>
+          <t>100,74; 291,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 114,13</t>
+          <t>-15,77; 111,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,13; 166,56</t>
+          <t>17,22; 163,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>138,67; 348,17</t>
+          <t>141,45; 369,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 90,11</t>
+          <t>0,35; 82,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,95; 95,3</t>
+          <t>5,01; 91,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>141,96; 280,16</t>
+          <t>135,5; 271,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 36,79</t>
+          <t>-25,51; 35,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 23,44</t>
+          <t>-35,93; 23,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,75; 84,91</t>
+          <t>32,18; 83,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 38,39</t>
+          <t>-21,82; 39,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 14,53</t>
+          <t>-40,61; 16,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,05; 71,37</t>
+          <t>20,32; 72,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 29,42</t>
+          <t>-13,27; 30,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 10,25</t>
+          <t>-28,4; 11,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36,94; 72,45</t>
+          <t>36,77; 72,95</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 235,09</t>
+          <t>-47,53; 224,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,3; 157,9</t>
+          <t>-60,14; 167,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47,78; 622,53</t>
+          <t>50,63; 596,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 167,96</t>
+          <t>-33,25; 187,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,5; 61,69</t>
+          <t>-60,72; 86,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,1; 311,05</t>
+          <t>27,48; 363,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 121,43</t>
+          <t>-25,61; 121,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 50,07</t>
+          <t>-51,53; 48,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>64,82; 313,07</t>
+          <t>66,51; 322,84</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 22,81</t>
+          <t>-10,59; 22,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 27,17</t>
+          <t>-9,75; 25,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53,93; 78,05</t>
+          <t>50,68; 76,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 16,09</t>
+          <t>-12,51; 16,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 20,85</t>
+          <t>-12,82; 21,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,63; 76,17</t>
+          <t>53,34; 75,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 14,66</t>
+          <t>-5,92; 14,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 18,39</t>
+          <t>-5,65; 18,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56,86; 73,2</t>
+          <t>56,54; 73,17</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 123,44</t>
+          <t>-33,94; 118,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 141,39</t>
+          <t>-28,31; 135,14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>149,06; 459,29</t>
+          <t>130,56; 470,8</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,43; 88,15</t>
+          <t>-40,25; 90,67</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-41,53; 108,2</t>
+          <t>-42,85; 110,97</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>156,14; 462,44</t>
+          <t>146,65; 430,68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 74,44</t>
+          <t>-20,65; 71,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 86,28</t>
+          <t>-19,73; 88,23</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>169,88; 364,55</t>
+          <t>170,91; 375,33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 1,71</t>
+          <t>-18,45; 2,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 4,97</t>
+          <t>-15,72; 4,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>37,98; 57,6</t>
+          <t>38,66; 58,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-26,45; -6,22</t>
+          <t>-27,1; -5,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-21,3; -0,84</t>
+          <t>-21,13; -0,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,78; 54,05</t>
+          <t>35,89; 54,1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-19,5; -6,09</t>
+          <t>-19,71; -5,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -1,74</t>
+          <t>-14,83; -1,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>40,19; 53,43</t>
+          <t>40,8; 53,56</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 6,09</t>
+          <t>-41,3; 8,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 15,02</t>
+          <t>-35,63; 14,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>84,15; 175,85</t>
+          <t>86,83; 184,36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-57,08; -16,96</t>
+          <t>-58,04; -16,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-45,66; -1,57</t>
+          <t>-46,42; -3,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>75,62; 159,35</t>
+          <t>77,86; 159,28</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-44,85; -16,11</t>
+          <t>-45,56; -16,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,05; -4,59</t>
+          <t>-34,47; -2,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>90,56; 153,89</t>
+          <t>90,92; 151,43</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 5,49</t>
+          <t>-15,83; 5,75</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 5,44</t>
+          <t>-16,35; 4,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>30,93; 50,54</t>
+          <t>29,33; 49,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 2,62</t>
+          <t>-18,08; 2,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -1,23</t>
+          <t>-21,24; -0,02</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,1; 44,37</t>
+          <t>25,9; 46,24</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 0,61</t>
+          <t>-14,26; 0,45</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -2,83</t>
+          <t>-16,25; -1,75</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>30,45; 44,68</t>
+          <t>30,54; 44,97</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 19,49</t>
+          <t>-39,69; 20,12</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 18,99</t>
+          <t>-40,6; 15,4</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>73,98; 187,82</t>
+          <t>68,88; 180,37</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 7,89</t>
+          <t>-38,51; 7,0</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-46,03; -3,76</t>
+          <t>-46,49; -0,08</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>53,63; 131,48</t>
+          <t>54,55; 138,92</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 2,25</t>
+          <t>-33,85; 1,35</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,31; -7,56</t>
+          <t>-38,62; -4,92</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>71,67; 134,27</t>
+          <t>72,04; 136,99</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,2</t>
+          <t>-5,96; 4,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,52</t>
+          <t>-7,44; 2,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>45,29; 54,56</t>
+          <t>46,21; 54,72</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,28</t>
+          <t>-7,0; 2,52</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,71</t>
+          <t>-7,09; 2,08</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>46,15; 54,12</t>
+          <t>46,52; 54,27</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,99</t>
+          <t>-4,86; 1,97</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,69</t>
+          <t>-6,07; 0,52</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>47,46; 53,16</t>
+          <t>47,18; 53,37</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 12,82</t>
+          <t>-15,9; 11,94</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 4,43</t>
+          <t>-20,07; 6,49</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>115,97; 169,33</t>
+          <t>120,52; 167,99</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 6,92</t>
+          <t>-18,68; 7,94</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 5,34</t>
+          <t>-18,7; 6,28</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>118,28; 165,08</t>
+          <t>121,04; 166,46</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 6,01</t>
+          <t>-12,96; 5,72</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 2,12</t>
+          <t>-16,37; 1,51</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>126,38; 159,12</t>
+          <t>125,01; 159,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 29,64</t>
+          <t>-8,09; 29,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 12,47</t>
+          <t>-18,58; 11,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,1; 57,27</t>
+          <t>19,96; 56,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 27,85</t>
+          <t>-5,86; 28,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 29,51</t>
+          <t>-3,7; 29,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,67; 57,5</t>
+          <t>28,77; 57,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 23,19</t>
+          <t>-2,05; 23,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 16,04</t>
+          <t>-4,92; 15,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,57; 53,06</t>
+          <t>29,83; 53,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 106,99</t>
+          <t>-20,44; 110,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 46,65</t>
+          <t>-44,37; 43,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,04; 219,23</t>
+          <t>52,06; 212,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 109,18</t>
+          <t>-15,73; 112,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 117,95</t>
+          <t>-10,18; 118,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,06; 234,83</t>
+          <t>65,44; 247,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 78,84</t>
+          <t>-4,94; 81,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 55,42</t>
+          <t>-12,76; 56,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,49; 191,04</t>
+          <t>76,82; 197,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 4,31</t>
+          <t>-23,97; 4,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 5,92</t>
+          <t>-20,44; 4,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,78; 61,68</t>
+          <t>39,83; 60,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 26,5</t>
+          <t>-3,51; 24,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 14,7</t>
+          <t>-11,6; 13,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,39; 68,28</t>
+          <t>46,87; 67,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 11,15</t>
+          <t>-9,63; 9,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 5,99</t>
+          <t>-11,96; 5,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,33; 61,32</t>
+          <t>46,84; 60,98</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,94; 12,17</t>
+          <t>-50,1; 12,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,23; 15,44</t>
+          <t>-41,3; 13,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,17; 190,79</t>
+          <t>78,53; 178,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 96,3</t>
+          <t>-7,88; 81,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 51,99</t>
+          <t>-28,08; 48,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100,63; 251,62</t>
+          <t>99,24; 240,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 32,08</t>
+          <t>-21,44; 27,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 17,1</t>
+          <t>-27,21; 16,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100,56; 188,57</t>
+          <t>101,51; 183,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 21,07</t>
+          <t>-8,31; 21,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 14,69</t>
+          <t>-16,39; 12,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,68; 67,95</t>
+          <t>44,37; 68,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 4,74</t>
+          <t>-20,5; 5,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,13; -1,76</t>
+          <t>-26,42; -1,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,64; 65,32</t>
+          <t>44,7; 66,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 7,99</t>
+          <t>-11,68; 8,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 2,16</t>
+          <t>-16,94; 2,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,18; 63,6</t>
+          <t>48,52; 64,22</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 79,25</t>
+          <t>-20,71; 77,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 58,31</t>
+          <t>-40,16; 49,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>108,48; 278,0</t>
+          <t>101,2; 279,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 18,0</t>
+          <t>-49,15; 16,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,88; -5,25</t>
+          <t>-62,07; -2,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97,9; 227,76</t>
+          <t>97,98; 238,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 26,52</t>
+          <t>-28,44; 27,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 7,58</t>
+          <t>-42,86; 6,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112,12; 215,78</t>
+          <t>114,09; 215,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 27,65</t>
+          <t>-2,0; 26,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 21,13</t>
+          <t>-9,49; 20,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,54; 65,44</t>
+          <t>39,18; 63,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 23,62</t>
+          <t>-4,76; 23,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 35,25</t>
+          <t>5,72; 34,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,21; 72,44</t>
+          <t>48,73; 70,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 21,14</t>
+          <t>1,3; 21,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 22,96</t>
+          <t>1,64; 23,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,37; 64,99</t>
+          <t>49,44; 66,14</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 115,74</t>
+          <t>-6,83; 106,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 88,13</t>
+          <t>-26,5; 83,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100,74; 291,23</t>
+          <t>96,06; 260,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 111,62</t>
+          <t>-15,17; 107,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,22; 163,13</t>
+          <t>16,78; 152,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>141,45; 369,56</t>
+          <t>141,92; 352,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 82,02</t>
+          <t>3,37; 84,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 91,88</t>
+          <t>4,38; 91,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>135,5; 271,45</t>
+          <t>142,58; 275,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 35,49</t>
+          <t>-27,49; 34,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 23,18</t>
+          <t>-36,45; 20,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,18; 83,8</t>
+          <t>34,88; 84,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 39,85</t>
+          <t>-23,21; 36,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 16,6</t>
+          <t>-38,61; 14,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,32; 72,21</t>
+          <t>23,14; 72,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 30,23</t>
+          <t>-14,31; 30,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-28,4; 11,45</t>
+          <t>-27,56; 13,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36,77; 72,95</t>
+          <t>35,61; 71,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 224,97</t>
+          <t>-49,16; 208,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,14; 167,53</t>
+          <t>-63,33; 135,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50,63; 596,9</t>
+          <t>57,16; 609,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 187,0</t>
+          <t>-36,5; 149,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,72; 86,24</t>
+          <t>-63,34; 70,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,48; 363,13</t>
+          <t>34,93; 390,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 121,88</t>
+          <t>-26,68; 130,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,53; 48,37</t>
+          <t>-50,41; 60,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>66,51; 322,84</t>
+          <t>60,52; 314,23</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 22,33</t>
+          <t>-11,75; 20,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 25,58</t>
+          <t>-9,36; 26,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50,68; 76,83</t>
+          <t>52,25; 77,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 16,03</t>
+          <t>-12,51; 16,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 21,08</t>
+          <t>-12,62; 22,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,34; 75,38</t>
+          <t>54,36; 75,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 14,98</t>
+          <t>-8,05; 14,71</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 18,8</t>
+          <t>-5,7; 18,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56,54; 73,17</t>
+          <t>56,21; 72,71</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 118,08</t>
+          <t>-32,76; 103,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 135,14</t>
+          <t>-29,26; 136,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>130,56; 470,8</t>
+          <t>141,76; 483,25</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-40,25; 90,67</t>
+          <t>-41,2; 86,78</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 110,97</t>
+          <t>-41,3; 110,32</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>146,65; 430,68</t>
+          <t>152,68; 445,86</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 71,45</t>
+          <t>-26,51; 65,87</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 88,23</t>
+          <t>-19,93; 86,62</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>170,91; 375,33</t>
+          <t>173,15; 369,4</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 2,41</t>
+          <t>-18,95; 1,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 4,8</t>
+          <t>-15,45; 5,03</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38,66; 58,01</t>
+          <t>38,6; 57,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-27,1; -5,86</t>
+          <t>-26,44; -6,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-21,13; -0,82</t>
+          <t>-20,77; -0,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,89; 54,1</t>
+          <t>35,44; 54,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-19,71; -5,78</t>
+          <t>-19,35; -4,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,83; -1,06</t>
+          <t>-14,78; 0,07</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>40,8; 53,56</t>
+          <t>40,58; 53,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 8,48</t>
+          <t>-44,58; 3,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 14,72</t>
+          <t>-34,71; 16,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>86,83; 184,36</t>
+          <t>84,06; 179,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-58,04; -16,88</t>
+          <t>-57,37; -17,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-46,42; -3,02</t>
+          <t>-45,82; -2,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>77,86; 159,28</t>
+          <t>74,41; 156,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-45,56; -16,57</t>
+          <t>-45,38; -14,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,47; -2,9</t>
+          <t>-34,25; 0,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>90,92; 151,43</t>
+          <t>91,85; 154,15</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 5,75</t>
+          <t>-15,73; 5,41</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 4,13</t>
+          <t>-16,69; 3,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>29,33; 49,45</t>
+          <t>29,65; 50,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 2,51</t>
+          <t>-18,42; 3,04</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-21,24; -0,02</t>
+          <t>-21,5; -1,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,9; 46,24</t>
+          <t>25,02; 44,36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 0,45</t>
+          <t>-14,1; 0,93</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -1,75</t>
+          <t>-16,41; -2,08</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>30,54; 44,97</t>
+          <t>30,65; 44,44</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 20,12</t>
+          <t>-37,87; 19,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-40,6; 15,4</t>
+          <t>-41,47; 11,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>68,88; 180,37</t>
+          <t>70,69; 181,02</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 7,0</t>
+          <t>-39,71; 8,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-46,49; -0,08</t>
+          <t>-46,4; -4,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>54,55; 138,92</t>
+          <t>53,1; 132,48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 1,35</t>
+          <t>-34,11; 2,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-38,62; -4,92</t>
+          <t>-39,25; -6,34</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>72,04; 136,99</t>
+          <t>71,54; 134,55</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 4,02</t>
+          <t>-6,15; 3,87</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 2,15</t>
+          <t>-7,17; 2,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>46,21; 54,72</t>
+          <t>45,7; 55,15</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 2,52</t>
+          <t>-6,69; 2,73</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,08</t>
+          <t>-6,88; 2,56</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>46,52; 54,27</t>
+          <t>46,23; 54,45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,97</t>
+          <t>-4,78; 2,22</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 0,52</t>
+          <t>-6,36; 0,38</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>47,18; 53,37</t>
+          <t>47,43; 53,5</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 11,94</t>
+          <t>-16,22; 11,55</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 6,49</t>
+          <t>-19,14; 6,48</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>120,52; 167,99</t>
+          <t>118,79; 173,53</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 7,94</t>
+          <t>-17,66; 8,13</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 6,28</t>
+          <t>-18,53; 7,6</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>121,04; 166,46</t>
+          <t>119,8; 167,91</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 5,72</t>
+          <t>-12,91; 6,75</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 1,51</t>
+          <t>-17,18; 1,16</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>125,01; 159,86</t>
+          <t>126,73; 161,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,97</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46,62</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>10,33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,02</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,97</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,6</t>
+          <t>49,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43,29</t>
+          <t>47,81</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 29,71</t>
+          <t>-4,96; 29,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 11,88</t>
+          <t>-3,05; 29,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,96; 56,14</t>
+          <t>32,83; 59,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 28,42</t>
+          <t>-8,5; 28,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 29,54</t>
+          <t>-18,91; 11,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,77; 57,35</t>
+          <t>34,47; 61,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 23,02</t>
+          <t>-0,95; 25,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 15,66</t>
+          <t>-6,24; 16,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,83; 53,86</t>
+          <t>37,64; 57,5</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39,57%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142,29%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>29,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-8,6%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>119,43%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>39,57%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>136,13%</t>
+          <t>140,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>127,8%</t>
+          <t>141,15%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 110,33</t>
+          <t>-13,45; 119,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 43,94</t>
+          <t>-8,47; 120,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,06; 212,52</t>
+          <t>75,63; 254,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 112,77</t>
+          <t>-21,76; 103,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 118,15</t>
+          <t>-44,6; 41,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,44; 247,98</t>
+          <t>78,26; 251,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 81,8</t>
+          <t>-2,82; 89,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 56,26</t>
+          <t>-15,4; 60,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,82; 197,54</t>
+          <t>91,22; 220,12</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,02</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>57,83</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-10,18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-7,48</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50,59</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,99</t>
+          <t>49,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>54,23</t>
+          <t>53,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 4,62</t>
+          <t>-4,06; 25,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 4,93</t>
+          <t>-12,43; 13,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,83; 60,83</t>
+          <t>46,28; 67,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 24,71</t>
+          <t>-23,67; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 13,78</t>
+          <t>-19,9; 4,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,87; 67,33</t>
+          <t>38,06; 59,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 9,67</t>
+          <t>-9,21; 10,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 5,88</t>
+          <t>-13,32; 5,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,84; 60,98</t>
+          <t>45,27; 60,54</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29,93%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>157,07%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-24,04%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-17,65%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>119,41%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,93%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>157,53%</t>
+          <t>116,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>136,77%</t>
+          <t>135,19%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,1; 12,44</t>
+          <t>-9,02; 88,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 13,66</t>
+          <t>-28,81; 46,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,53; 178,42</t>
+          <t>98,23; 232,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 81,53</t>
+          <t>-49,46; 12,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 48,54</t>
+          <t>-42,19; 14,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,24; 240,69</t>
+          <t>72,94; 178,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 27,2</t>
+          <t>-21,79; 30,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 16,53</t>
+          <t>-30,06; 17,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>101,51; 183,25</t>
+          <t>98,56; 185,09</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-7,96</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-13,63</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55,93</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,96</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>57,15</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,96</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-13,63</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,52</t>
+          <t>56,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56,88</t>
+          <t>56,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 21,44</t>
+          <t>-22,16; 5,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 12,85</t>
+          <t>-24,69; -1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,37; 68,06</t>
+          <t>45,05; 66,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 5,87</t>
+          <t>-7,68; 21,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,42; -1,35</t>
+          <t>-15,47; 13,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,7; 66,9</t>
+          <t>44,31; 66,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 8,72</t>
+          <t>-10,85; 8,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 2,03</t>
+          <t>-16,89; 1,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,52; 64,22</t>
+          <t>48,18; 62,75</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-21,68%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-37,12%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152,33%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19,86%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-2,83%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>169,42%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-21,68%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-37,12%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>153,92%</t>
+          <t>168,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>161,31%</t>
+          <t>159,72%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 77,68</t>
+          <t>-52,6; 17,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 49,98</t>
+          <t>-58,03; -3,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101,2; 279,59</t>
+          <t>99,2; 237,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,15; 16,89</t>
+          <t>-18,95; 82,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,07; -2,61</t>
+          <t>-37,29; 51,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97,98; 238,37</t>
+          <t>103,47; 263,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 27,9</t>
+          <t>-26,92; 28,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 6,58</t>
+          <t>-42,24; 3,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>114,09; 215,62</t>
+          <t>117,26; 213,83</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20,17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59,2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12,68</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5,37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53,78</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20,17</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,61</t>
+          <t>54,19</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>57,38</t>
+          <t>56,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 26,66</t>
+          <t>-4,64; 23,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 20,63</t>
+          <t>6,5; 34,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,18; 63,91</t>
+          <t>46,66; 71,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 23,4</t>
+          <t>-2,86; 27,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,72; 34,67</t>
+          <t>-8,67; 20,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,73; 70,89</t>
+          <t>40,87; 65,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 21,32</t>
+          <t>1,12; 21,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 23,07</t>
+          <t>2,56; 23,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,44; 66,14</t>
+          <t>48,01; 65,38</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35,08%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>74,18%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>217,78%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>40,06%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>16,98%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>169,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>35,08%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>74,18%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>222,96%</t>
+          <t>171,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>195,83%</t>
+          <t>193,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 106,39</t>
+          <t>-14,12; 114,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 83,72</t>
+          <t>17,13; 166,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96,06; 260,22</t>
+          <t>134,05; 338,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 107,69</t>
+          <t>-8,31; 107,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,78; 152,95</t>
+          <t>-24,11; 79,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>141,92; 352,66</t>
+          <t>99,56; 270,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 84,09</t>
+          <t>2,96; 90,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,38; 91,2</t>
+          <t>7,95; 95,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>142,58; 275,5</t>
+          <t>138,46; 277,23</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,18</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-11,65</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>48,99</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,09</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>61,63</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10,18</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-11,65</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,2</t>
+          <t>61,85</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>54,88</t>
+          <t>54,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 34,63</t>
+          <t>-20,0; 38,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 20,86</t>
+          <t>-40,67; 14,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34,88; 84,03</t>
+          <t>23,05; 71,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 36,98</t>
+          <t>-26,09; 36,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,61; 14,66</t>
+          <t>-33,01; 23,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,14; 72,63</t>
+          <t>29,97; 85,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 30,61</t>
+          <t>-15,49; 29,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 13,78</t>
+          <t>-27,96; 10,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35,61; 71,33</t>
+          <t>36,95; 72,51</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-27,17%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>114,23%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>17,58%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-8,75%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>174,45%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>23,73%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-27,17%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>114,7%</t>
+          <t>175,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>139,12%</t>
+          <t>139,3%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 208,93</t>
+          <t>-33,36; 167,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 135,59</t>
+          <t>-64,5; 61,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57,16; 609,46</t>
+          <t>36,2; 305,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 149,9</t>
+          <t>-50,05; 235,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 70,88</t>
+          <t>-57,3; 157,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,93; 390,87</t>
+          <t>47,53; 617,95</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 130,65</t>
+          <t>-28,59; 121,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 60,13</t>
+          <t>-51,27; 50,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>60,52; 314,23</t>
+          <t>64,99; 313,78</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1,47</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>64,7</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>6,24</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>7,92</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>65,7</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65,36</t>
+          <t>66,45</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>65,49</t>
+          <t>65,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 20,87</t>
+          <t>-12,86; 16,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 26,03</t>
+          <t>-12,42; 20,85</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52,25; 77,03</t>
+          <t>52,33; 75,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 16,62</t>
+          <t>-8,47; 22,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 22,09</t>
+          <t>-9,1; 27,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,36; 75,54</t>
+          <t>55,18; 78,01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 14,71</t>
+          <t>-6,43; 14,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 18,94</t>
+          <t>-6,19; 18,39</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56,21; 72,71</t>
+          <t>57,02; 73,3</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>254,47%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>23,47%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>29,8%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>247,09%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>257,08%</t>
+          <t>249,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>252,13%</t>
+          <t>252,41%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-32,76; 103,83</t>
+          <t>-39,43; 88,15</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 136,02</t>
+          <t>-41,53; 108,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>141,76; 483,25</t>
+          <t>153,87; 459,0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 86,78</t>
+          <t>-28,14; 123,44</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 110,32</t>
+          <t>-30,37; 141,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>152,68; 445,86</t>
+          <t>150,5; 461,26</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 65,87</t>
+          <t>-21,68; 74,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 86,62</t>
+          <t>-21,25; 86,28</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>173,15; 369,4</t>
+          <t>169,63; 362,56</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-16,53</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-10,83</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>44,83</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-8,29</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-4,8</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>49,16</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-16,53</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-10,83</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,3</t>
+          <t>51,02</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>47,13</t>
+          <t>47,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 1,52</t>
+          <t>-26,45; -6,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 5,03</t>
+          <t>-21,3; -0,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38,6; 57,81</t>
+          <t>33,89; 53,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-26,44; -6,28</t>
+          <t>-19,27; 1,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -0,59</t>
+          <t>-15,7; 4,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,44; 54,06</t>
+          <t>40,88; 59,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-19,35; -4,99</t>
+          <t>-19,5; -6,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 0,07</t>
+          <t>-15,13; -1,74</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>40,58; 53,79</t>
+          <t>40,91; 53,97</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-40,53%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-26,57%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>109,94%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-21,37%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-12,37%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>126,74%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-40,53%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-26,57%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>111,09%</t>
+          <t>131,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>118,45%</t>
+          <t>120,07%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 3,94</t>
+          <t>-57,08; -16,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 16,29</t>
+          <t>-45,66; -1,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>84,06; 179,53</t>
+          <t>74,47; 156,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -17,89</t>
+          <t>-42,38; 6,09</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-45,82; -2,0</t>
+          <t>-34,69; 15,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>74,41; 156,63</t>
+          <t>90,4; 185,07</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-45,38; -14,83</t>
+          <t>-44,85; -16,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 0,08</t>
+          <t>-35,05; -4,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>91,85; 154,15</t>
+          <t>91,81; 155,36</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-7,89</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-11,51</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>35,67</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-5,2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-6,38</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>39,99</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-7,89</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-11,51</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,52</t>
+          <t>40,34</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>37,74</t>
+          <t>37,96</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 5,41</t>
+          <t>-17,76; 2,62</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 3,14</t>
+          <t>-21,05; -1,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>29,65; 50,27</t>
+          <t>24,98; 44,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 3,04</t>
+          <t>-16,21; 5,49</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-21,5; -1,04</t>
+          <t>-16,23; 5,44</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,02; 44,36</t>
+          <t>31,14; 51,11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 0,93</t>
+          <t>-13,91; 0,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,41; -2,08</t>
+          <t>-16,75; -2,83</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>30,65; 44,44</t>
+          <t>30,73; 44,87</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-19,18%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-27,98%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>86,68%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-15,06%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-18,48%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>115,87%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-19,18%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-27,98%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>116,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>100,03%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 19,67</t>
+          <t>-37,67; 7,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 11,25</t>
+          <t>-46,03; -3,76</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>70,69; 181,02</t>
+          <t>53,11; 132,57</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 8,2</t>
+          <t>-38,56; 19,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-46,4; -4,1</t>
+          <t>-39,57; 18,99</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>53,1; 132,48</t>
+          <t>74,7; 187,49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 2,5</t>
+          <t>-33,57; 2,25</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,25; -6,34</t>
+          <t>-39,31; -7,56</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>71,54; 134,55</t>
+          <t>71,94; 133,69</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-2,61</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>50,18</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-2,83</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>50,43</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>50,47</t>
+          <t>51,17</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>50,46</t>
+          <t>50,66</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,87</t>
+          <t>-7,64; 2,28</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,15</t>
+          <t>-7,6; 1,71</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>45,7; 55,15</t>
+          <t>45,66; 53,86</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,73</t>
+          <t>-5,59; 4,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,56</t>
+          <t>-7,89; 1,52</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>46,23; 54,45</t>
+          <t>46,14; 55,15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,22</t>
+          <t>-5,01; 1,99</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,38</t>
+          <t>-5,93; 0,69</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>47,43; 53,5</t>
+          <t>47,75; 53,13</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-5,44%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-7,32%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>140,57%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-2,83%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-7,99%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>142,58%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-5,44%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-7,32%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>141,39%</t>
+          <t>144,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>141,99%</t>
+          <t>142,54%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 11,55</t>
+          <t>-20,19; 6,92</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 6,48</t>
+          <t>-19,78; 5,34</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>118,79; 173,53</t>
+          <t>117,16; 164,09</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 8,13</t>
+          <t>-14,93; 12,82</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 7,6</t>
+          <t>-21,13; 4,43</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>119,8; 167,91</t>
+          <t>118,38; 170,64</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 6,75</t>
+          <t>-13,32; 6,01</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 1,16</t>
+          <t>-16,0; 2,12</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>126,73; 161,12</t>
+          <t>127,14; 159,94</t>
         </is>
       </c>
     </row>
